--- a/analyst/Tracy/rmonize/data_proc_elem/DPE_DEGS1_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_proc_elem/DPE_DEGS1_TRACY.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_proc_elem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57651AD7-FEFD-4B8F-874F-363B38E1C756}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C70A5D-DF7D-49B7-BA2B-A4252D99EF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -141,9 +141,6 @@
     <t>Highest level of education [ISCED 2011]</t>
   </si>
   <si>
-    <t xml:space="preserve">(1=1;2=2;3=3;4=3;5=4;6=6;7=7;8=8) </t>
-  </si>
-  <si>
     <t>ISCED-97 5A has been mapped to Master's level as it is described to be primarily driven by academic institutions, whereas 5B has been mapped to the Bachelor's level as level 5B in 1997 was characterised by being related to practical work and education</t>
   </si>
   <si>
@@ -153,10 +150,13 @@
     <t>RCstat_k</t>
   </si>
   <si>
-    <t xml:space="preserve">(1=3;2=2;3=1;ELSE=4) </t>
-  </si>
-  <si>
     <t>Rauchstatus in 3 Kategorien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recode(1=1;2=2;3=3;4=3;5=4;6=6;7=7;8=8) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">recode(1=3;2=2;3=1;ELSE=4) </t>
   </si>
 </sst>
 </file>
@@ -237,9 +237,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -277,9 +277,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -312,26 +312,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,26 +347,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -715,16 +681,16 @@
         <v>31</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="J5" t="s">
         <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -770,16 +736,16 @@
         <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
         <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="J7" t="s">
         <v>25</v>
